--- a/Babila2022_MgCa_SDB_PETM.xlsx
+++ b/Babila2022_MgCa_SDB_PETM.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="17">
   <si>
     <t xml:space="preserve">Species</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t xml:space="preserve">Mg/Ca mmol/mol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ph_corr_mgca</t>
   </si>
   <si>
     <t xml:space="preserve">expoConstant_A</t>
@@ -355,11 +358,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="84.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -375,7 +379,7 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -402,10 +406,13 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" s="5" t="n">
         <v>688.55</v>
@@ -417,40 +424,41 @@
       <c r="D2" s="6" t="n">
         <v>3.37770637043789</v>
       </c>
-      <c r="E2" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E2" s="6"/>
       <c r="F2" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G2" s="1" t="n">
-        <f aca="false">LN(D2/F2)/E2</f>
+        <v>0.52</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <f aca="false">LN(D2/G2)/F2</f>
         <v>31.1853892988045</v>
       </c>
-      <c r="H2" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I2" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J2" s="1" t="n">
-        <f aca="false">LN(D2/I2)/H2</f>
+        <v>0.55</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <f aca="false">LN(D2/J2)/I2</f>
         <v>25.9290555896747</v>
       </c>
-      <c r="K2" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L2" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M2" s="1" t="n">
-        <f aca="false">LN(D2/L2)/K2</f>
+        <v>0.5</v>
+      </c>
+      <c r="N2" s="1" t="n">
+        <f aca="false">LN(D2/M2)/L2</f>
         <v>38.2068814216311</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="5" t="n">
         <v>686.05</v>
@@ -462,40 +470,41 @@
       <c r="D3" s="6" t="n">
         <v>3.32132203023</v>
       </c>
-      <c r="E3" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E3" s="6"/>
       <c r="F3" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G3" s="1" t="n">
-        <f aca="false">LN(D3/F3)/E3</f>
+        <v>0.52</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <f aca="false">LN(D3/G3)/F3</f>
         <v>30.904822882504</v>
       </c>
-      <c r="H3" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I3" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J3" s="1" t="n">
-        <f aca="false">LN(D3/I3)/H3</f>
+        <v>0.55</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <f aca="false">LN(D3/J3)/I3</f>
         <v>25.6885700899885</v>
       </c>
-      <c r="K3" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L3" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M3" s="1" t="n">
-        <f aca="false">LN(D3/L3)/K3</f>
+        <v>0.5</v>
+      </c>
+      <c r="N3" s="1" t="n">
+        <f aca="false">LN(D3/M3)/L3</f>
         <v>37.8702017220704</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="5" t="n">
         <v>679.55</v>
@@ -507,40 +516,41 @@
       <c r="D4" s="6" t="n">
         <v>3.77293722597061</v>
       </c>
-      <c r="E4" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E4" s="6"/>
       <c r="F4" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G4" s="1" t="n">
-        <f aca="false">LN(D4/F4)/E4</f>
+        <v>0.52</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <f aca="false">LN(D4/G4)/F4</f>
         <v>33.0296711758966</v>
       </c>
-      <c r="H4" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I4" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J4" s="1" t="n">
-        <f aca="false">LN(D4/I4)/H4</f>
+        <v>0.55</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <f aca="false">LN(D4/J4)/I4</f>
         <v>27.5098686271822</v>
       </c>
-      <c r="K4" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L4" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M4" s="1" t="n">
-        <f aca="false">LN(D4/L4)/K4</f>
+        <v>0.5</v>
+      </c>
+      <c r="N4" s="1" t="n">
+        <f aca="false">LN(D4/M4)/L4</f>
         <v>40.4200196741416</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="5" t="n">
         <v>675.3</v>
@@ -552,40 +562,41 @@
       <c r="D5" s="6" t="n">
         <v>3.80168242018434</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E5" s="6"/>
       <c r="F5" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G5" s="1" t="n">
-        <f aca="false">LN(D5/F5)/E5</f>
+        <v>0.52</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <f aca="false">LN(D5/G5)/F5</f>
         <v>33.1561696385231</v>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I5" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J5" s="1" t="n">
-        <f aca="false">LN(D5/I5)/H5</f>
+        <v>0.55</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <f aca="false">LN(D5/J5)/I5</f>
         <v>27.6182958808621</v>
       </c>
-      <c r="K5" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L5" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M5" s="1" t="n">
-        <f aca="false">LN(D5/L5)/K5</f>
+        <v>0.5</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <f aca="false">LN(D5/M5)/L5</f>
         <v>40.5718178292934</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="5" t="n">
         <v>673.05</v>
@@ -597,40 +608,41 @@
       <c r="D6" s="6" t="n">
         <v>3.15511358720585</v>
       </c>
-      <c r="E6" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E6" s="6"/>
       <c r="F6" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G6" s="1" t="n">
-        <f aca="false">LN(D6/F6)/E6</f>
+        <v>0.52</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <f aca="false">LN(D6/G6)/F6</f>
         <v>30.0491827505953</v>
       </c>
-      <c r="H6" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I6" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J6" s="1" t="n">
-        <f aca="false">LN(D6/I6)/H6</f>
+        <v>0.55</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <f aca="false">LN(D6/J6)/I6</f>
         <v>24.9551642626382</v>
       </c>
-      <c r="K6" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L6" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M6" s="1" t="n">
-        <f aca="false">LN(D6/L6)/K6</f>
+        <v>0.5</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <f aca="false">LN(D6/M6)/L6</f>
         <v>36.84343356378</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="5" t="n">
         <v>671.35</v>
@@ -642,40 +654,41 @@
       <c r="D7" s="6" t="n">
         <v>3.47852709871862</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E7" s="6"/>
       <c r="F7" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G7" s="1" t="n">
-        <f aca="false">LN(D7/F7)/E7</f>
+        <v>0.52</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <f aca="false">LN(D7/G7)/F7</f>
         <v>31.6755904017316</v>
       </c>
-      <c r="H7" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I7" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J7" s="1" t="n">
-        <f aca="false">LN(D7/I7)/H7</f>
+        <v>0.55</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <f aca="false">LN(D7/J7)/I7</f>
         <v>26.3492279636122</v>
       </c>
-      <c r="K7" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L7" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M7" s="1" t="n">
-        <f aca="false">LN(D7/L7)/K7</f>
+        <v>0.5</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <f aca="false">LN(D7/M7)/L7</f>
         <v>38.7951227451435</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="5" t="n">
         <v>663.05</v>
@@ -687,40 +700,41 @@
       <c r="D8" s="6" t="n">
         <v>4.81715464394159</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E8" s="6"/>
       <c r="F8" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G8" s="1" t="n">
-        <f aca="false">LN(D8/F8)/E8</f>
+        <v>0.52</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <f aca="false">LN(D8/G8)/F8</f>
         <v>37.1018316387725</v>
       </c>
-      <c r="H8" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I8" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J8" s="1" t="n">
-        <f aca="false">LN(D8/I8)/H8</f>
+        <v>0.55</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <f aca="false">LN(D8/J8)/I8</f>
         <v>31.0002918810758</v>
       </c>
-      <c r="K8" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L8" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M8" s="1" t="n">
-        <f aca="false">LN(D8/L8)/K8</f>
+        <v>0.5</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <f aca="false">LN(D8/M8)/L8</f>
         <v>45.3066122295927</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="n">
         <v>659.8</v>
@@ -732,40 +746,41 @@
       <c r="D9" s="6" t="n">
         <v>4.49456291223059</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E9" s="6"/>
       <c r="F9" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G9" s="1" t="n">
-        <f aca="false">LN(D9/F9)/E9</f>
+        <v>0.52</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <f aca="false">LN(D9/G9)/F9</f>
         <v>35.9465815323981</v>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I9" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J9" s="1" t="n">
-        <f aca="false">LN(D9/I9)/H9</f>
+        <v>0.55</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <f aca="false">LN(D9/J9)/I9</f>
         <v>30.0100775041834</v>
       </c>
-      <c r="K9" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L9" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M9" s="1" t="n">
-        <f aca="false">LN(D9/L9)/K9</f>
+        <v>0.5</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <f aca="false">LN(D9/M9)/L9</f>
         <v>43.9203121019433</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="5" t="n">
         <v>655.8</v>
@@ -777,40 +792,41 @@
       <c r="D10" s="6" t="n">
         <v>4.52679011590695</v>
       </c>
-      <c r="E10" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E10" s="6"/>
       <c r="F10" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G10" s="1" t="n">
-        <f aca="false">LN(D10/F10)/E10</f>
+        <v>0.52</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <f aca="false">LN(D10/G10)/F10</f>
         <v>36.0656595342089</v>
       </c>
-      <c r="H10" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I10" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J10" s="1" t="n">
-        <f aca="false">LN(D10/I10)/H10</f>
+        <v>0.55</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <f aca="false">LN(D10/J10)/I10</f>
         <v>30.1121443628784</v>
       </c>
-      <c r="K10" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L10" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M10" s="1" t="n">
-        <f aca="false">LN(D10/L10)/K10</f>
+        <v>0.5</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <f aca="false">LN(D10/M10)/L10</f>
         <v>44.0632057041163</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B11" s="5" t="n">
         <v>654.3</v>
@@ -822,40 +838,41 @@
       <c r="D11" s="6" t="n">
         <v>4.63952062909654</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E11" s="6"/>
       <c r="F11" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G11" s="1" t="n">
-        <f aca="false">LN(D11/F11)/E11</f>
+        <v>0.52</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <f aca="false">LN(D11/G11)/F11</f>
         <v>36.4756252602165</v>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I11" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J11" s="1" t="n">
-        <f aca="false">LN(D11/I11)/H11</f>
+        <v>0.55</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <f aca="false">LN(D11/J11)/I11</f>
         <v>30.4635435565993</v>
       </c>
-      <c r="K11" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L11" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M11" s="1" t="n">
-        <f aca="false">LN(D11/L11)/K11</f>
+        <v>0.5</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <f aca="false">LN(D11/M11)/L11</f>
         <v>44.5551645753255</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B12" s="5" t="n">
         <v>653.3</v>
@@ -867,40 +884,41 @@
       <c r="D12" s="6" t="n">
         <v>4.24366142677953</v>
       </c>
-      <c r="E12" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E12" s="6"/>
       <c r="F12" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G12" s="1" t="n">
-        <f aca="false">LN(D12/F12)/E12</f>
+        <v>0.52</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <f aca="false">LN(D12/G12)/F12</f>
         <v>34.9892151343775</v>
       </c>
-      <c r="H12" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I12" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J12" s="1" t="n">
-        <f aca="false">LN(D12/I12)/H12</f>
+        <v>0.55</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <f aca="false">LN(D12/J12)/I12</f>
         <v>29.1894777344516</v>
       </c>
-      <c r="K12" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L12" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M12" s="1" t="n">
-        <f aca="false">LN(D12/L12)/K12</f>
+        <v>0.5</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <f aca="false">LN(D12/M12)/L12</f>
         <v>42.7714724243187</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" s="5" t="n">
         <v>652.3</v>
@@ -912,40 +930,41 @@
       <c r="D13" s="6" t="n">
         <v>4.37449197864375</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E13" s="6"/>
       <c r="F13" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G13" s="1" t="n">
-        <f aca="false">LN(D13/F13)/E13</f>
+        <v>0.52</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <f aca="false">LN(D13/G13)/F13</f>
         <v>35.4952810217791</v>
       </c>
-      <c r="H13" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I13" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J13" s="1" t="n">
-        <f aca="false">LN(D13/I13)/H13</f>
+        <v>0.55</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <f aca="false">LN(D13/J13)/I13</f>
         <v>29.6232484950815</v>
       </c>
-      <c r="K13" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L13" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M13" s="1" t="n">
-        <f aca="false">LN(D13/L13)/K13</f>
+        <v>0.5</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <f aca="false">LN(D13/M13)/L13</f>
         <v>43.3787514892006</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="5" t="n">
         <v>645.55</v>
@@ -957,40 +976,41 @@
       <c r="D14" s="6" t="n">
         <v>4.59368079324879</v>
       </c>
-      <c r="E14" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E14" s="6"/>
       <c r="F14" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G14" s="1" t="n">
-        <f aca="false">LN(D14/F14)/E14</f>
+        <v>0.52</v>
+      </c>
+      <c r="H14" s="1" t="n">
+        <f aca="false">LN(D14/G14)/F14</f>
         <v>36.3101347642827</v>
       </c>
-      <c r="H14" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I14" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J14" s="1" t="n">
-        <f aca="false">LN(D14/I14)/H14</f>
+        <v>0.55</v>
+      </c>
+      <c r="K14" s="1" t="n">
+        <f aca="false">LN(D14/J14)/I14</f>
         <v>30.3216945600845</v>
       </c>
-      <c r="K14" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L14" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M14" s="1" t="n">
-        <f aca="false">LN(D14/L14)/K14</f>
+        <v>0.5</v>
+      </c>
+      <c r="N14" s="1" t="n">
+        <f aca="false">LN(D14/M14)/L14</f>
         <v>44.3565759802048</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="5" t="n">
         <v>631.75</v>
@@ -1002,40 +1022,41 @@
       <c r="D15" s="6" t="n">
         <v>4.09371228995758</v>
       </c>
-      <c r="E15" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E15" s="6"/>
       <c r="F15" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G15" s="1" t="n">
-        <f aca="false">LN(D15/F15)/E15</f>
+        <v>0.52</v>
+      </c>
+      <c r="H15" s="1" t="n">
+        <f aca="false">LN(D15/G15)/F15</f>
         <v>34.3896446025374</v>
       </c>
-      <c r="H15" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I15" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J15" s="1" t="n">
-        <f aca="false">LN(D15/I15)/H15</f>
+        <v>0.55</v>
+      </c>
+      <c r="K15" s="1" t="n">
+        <f aca="false">LN(D15/J15)/I15</f>
         <v>28.6755601357315</v>
       </c>
-      <c r="K15" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L15" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M15" s="1" t="n">
-        <f aca="false">LN(D15/L15)/K15</f>
+        <v>0.5</v>
+      </c>
+      <c r="N15" s="1" t="n">
+        <f aca="false">LN(D15/M15)/L15</f>
         <v>42.0519877861105</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" s="5" t="n">
         <v>624.45</v>
@@ -1047,40 +1068,41 @@
       <c r="D16" s="6" t="n">
         <v>3.80276117485422</v>
       </c>
-      <c r="E16" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E16" s="6"/>
       <c r="F16" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G16" s="1" t="n">
-        <f aca="false">LN(D16/F16)/E16</f>
+        <v>0.52</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <f aca="false">LN(D16/G16)/F16</f>
         <v>33.1608982539423</v>
       </c>
-      <c r="H16" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I16" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J16" s="1" t="n">
-        <f aca="false">LN(D16/I16)/H16</f>
+        <v>0.55</v>
+      </c>
+      <c r="K16" s="1" t="n">
+        <f aca="false">LN(D16/J16)/I16</f>
         <v>27.6223489797927</v>
       </c>
-      <c r="K16" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L16" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M16" s="1" t="n">
-        <f aca="false">LN(D16/L16)/K16</f>
+        <v>0.5</v>
+      </c>
+      <c r="N16" s="1" t="n">
+        <f aca="false">LN(D16/M16)/L16</f>
         <v>40.5774921677963</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" s="5" t="n">
         <v>618.8</v>
@@ -1092,40 +1114,41 @@
       <c r="D17" s="6" t="n">
         <v>3.34430466032453</v>
       </c>
-      <c r="E17" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E17" s="6"/>
       <c r="F17" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G17" s="1" t="n">
-        <f aca="false">LN(D17/F17)/E17</f>
+        <v>0.52</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <f aca="false">LN(D17/G17)/F17</f>
         <v>31.0197544172591</v>
       </c>
-      <c r="H17" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I17" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J17" s="1" t="n">
-        <f aca="false">LN(D17/I17)/H17</f>
+        <v>0.55</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <f aca="false">LN(D17/J17)/I17</f>
         <v>25.7870828340643</v>
       </c>
-      <c r="K17" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L17" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M17" s="1" t="n">
-        <f aca="false">LN(D17/L17)/K17</f>
+        <v>0.5</v>
+      </c>
+      <c r="N17" s="1" t="n">
+        <f aca="false">LN(D17/M17)/L17</f>
         <v>38.0081195637766</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B18" s="5" t="n">
         <v>615.65</v>
@@ -1137,40 +1160,41 @@
       <c r="D18" s="6" t="n">
         <v>3.99819429417759</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E18" s="6"/>
       <c r="F18" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G18" s="1" t="n">
-        <f aca="false">LN(D18/F18)/E18</f>
+        <v>0.52</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <f aca="false">LN(D18/G18)/F18</f>
         <v>33.9961550024559</v>
       </c>
-      <c r="H18" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I18" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J18" s="1" t="n">
-        <f aca="false">LN(D18/I18)/H18</f>
+        <v>0.55</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <f aca="false">LN(D18/J18)/I18</f>
         <v>28.3382833356616</v>
       </c>
-      <c r="K18" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L18" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M18" s="1" t="n">
-        <f aca="false">LN(D18/L18)/K18</f>
+        <v>0.5</v>
+      </c>
+      <c r="N18" s="1" t="n">
+        <f aca="false">LN(D18/M18)/L18</f>
         <v>41.5798002660127</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B19" s="5" t="n">
         <v>609.9</v>
@@ -1182,40 +1206,41 @@
       <c r="D19" s="6" t="n">
         <v>3.62902502104679</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E19" s="6"/>
       <c r="F19" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G19" s="1" t="n">
-        <f aca="false">LN(D19/F19)/E19</f>
+        <v>0.52</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <f aca="false">LN(D19/G19)/F19</f>
         <v>32.3815081727261</v>
       </c>
-      <c r="H19" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I19" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J19" s="1" t="n">
-        <f aca="false">LN(D19/I19)/H19</f>
+        <v>0.55</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <f aca="false">LN(D19/J19)/I19</f>
         <v>26.9543003387503</v>
       </c>
-      <c r="K19" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L19" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M19" s="1" t="n">
-        <f aca="false">LN(D19/L19)/K19</f>
+        <v>0.5</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <f aca="false">LN(D19/M19)/L19</f>
         <v>39.6422240703369</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B20" s="5" t="n">
         <v>599.2</v>
@@ -1227,40 +1252,41 @@
       <c r="D20" s="6" t="n">
         <v>3.65536466739638</v>
       </c>
-      <c r="E20" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E20" s="6"/>
       <c r="F20" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G20" s="1" t="n">
-        <f aca="false">LN(D20/F20)/E20</f>
+        <v>0.52</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <f aca="false">LN(D20/G20)/F20</f>
         <v>32.502038797216</v>
       </c>
-      <c r="H20" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I20" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J20" s="1" t="n">
-        <f aca="false">LN(D20/I20)/H20</f>
+        <v>0.55</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <f aca="false">LN(D20/J20)/I20</f>
         <v>27.0576123025988</v>
       </c>
-      <c r="K20" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L20" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M20" s="1" t="n">
-        <f aca="false">LN(D20/L20)/K20</f>
+        <v>0.5</v>
+      </c>
+      <c r="N20" s="1" t="n">
+        <f aca="false">LN(D20/M20)/L20</f>
         <v>39.7868608197249</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B21" s="8" t="n">
         <v>689.05</v>
@@ -1272,40 +1298,41 @@
       <c r="D21" s="9" t="n">
         <v>3.32952951737338</v>
       </c>
-      <c r="E21" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E21" s="9"/>
       <c r="F21" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G21" s="1" t="n">
-        <f aca="false">LN(D21/F21)/E21</f>
+        <v>0.52</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <f aca="false">LN(D21/G21)/F21</f>
         <v>30.9459579223857</v>
       </c>
-      <c r="H21" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I21" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J21" s="1" t="n">
-        <f aca="false">LN(D21/I21)/H21</f>
+        <v>0.55</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <f aca="false">LN(D21/J21)/I21</f>
         <v>25.7238286956014</v>
       </c>
-      <c r="K21" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L21" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M21" s="1" t="n">
-        <f aca="false">LN(D21/L21)/K21</f>
+        <v>0.5</v>
+      </c>
+      <c r="N21" s="1" t="n">
+        <f aca="false">LN(D21/M21)/L21</f>
         <v>37.9195637699284</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>686.05</v>
@@ -1317,40 +1344,41 @@
       <c r="D22" s="9" t="n">
         <v>3.33728323938866</v>
       </c>
-      <c r="E22" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E22" s="9"/>
       <c r="F22" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G22" s="1" t="n">
-        <f aca="false">LN(D22/F22)/E22</f>
+        <v>0.52</v>
+      </c>
+      <c r="H22" s="1" t="n">
+        <f aca="false">LN(D22/G22)/F22</f>
         <v>30.9847257004039</v>
       </c>
-      <c r="H22" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I22" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J22" s="1" t="n">
-        <f aca="false">LN(D22/I22)/H22</f>
+        <v>0.55</v>
+      </c>
+      <c r="K22" s="1" t="n">
+        <f aca="false">LN(D22/J22)/I22</f>
         <v>25.757058219617</v>
       </c>
-      <c r="K22" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L22" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M22" s="1" t="n">
-        <f aca="false">LN(D22/L22)/K22</f>
+        <v>0.5</v>
+      </c>
+      <c r="N22" s="1" t="n">
+        <f aca="false">LN(D22/M22)/L22</f>
         <v>37.9660851035503</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>679.55</v>
@@ -1362,40 +1390,41 @@
       <c r="D23" s="9" t="n">
         <v>3.51496415665291</v>
       </c>
-      <c r="E23" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E23" s="9"/>
       <c r="F23" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G23" s="1" t="n">
-        <f aca="false">LN(D23/F23)/E23</f>
+        <v>0.52</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <f aca="false">LN(D23/G23)/F23</f>
         <v>31.8492632560584</v>
       </c>
-      <c r="H23" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I23" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J23" s="1" t="n">
-        <f aca="false">LN(D23/I23)/H23</f>
+        <v>0.55</v>
+      </c>
+      <c r="K23" s="1" t="n">
+        <f aca="false">LN(D23/J23)/I23</f>
         <v>26.498090410178</v>
       </c>
-      <c r="K23" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L23" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M23" s="1" t="n">
-        <f aca="false">LN(D23/L23)/K23</f>
+        <v>0.5</v>
+      </c>
+      <c r="N23" s="1" t="n">
+        <f aca="false">LN(D23/M23)/L23</f>
         <v>39.0035301703357</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>675.3</v>
@@ -1407,40 +1436,41 @@
       <c r="D24" s="9" t="n">
         <v>3.92719600532461</v>
       </c>
-      <c r="E24" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E24" s="9"/>
       <c r="F24" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G24" s="1" t="n">
-        <f aca="false">LN(D24/F24)/E24</f>
+        <v>0.52</v>
+      </c>
+      <c r="H24" s="1" t="n">
+        <f aca="false">LN(D24/G24)/F24</f>
         <v>33.6975358997717</v>
       </c>
-      <c r="H24" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I24" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J24" s="1" t="n">
-        <f aca="false">LN(D24/I24)/H24</f>
+        <v>0.55</v>
+      </c>
+      <c r="K24" s="1" t="n">
+        <f aca="false">LN(D24/J24)/I24</f>
         <v>28.0823241047894</v>
       </c>
-      <c r="K24" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L24" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M24" s="1" t="n">
-        <f aca="false">LN(D24/L24)/K24</f>
+        <v>0.5</v>
+      </c>
+      <c r="N24" s="1" t="n">
+        <f aca="false">LN(D24/M24)/L24</f>
         <v>41.2214573427916</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>673.05</v>
@@ -1452,40 +1482,41 @@
       <c r="D25" s="9" t="n">
         <v>3.10214616402007</v>
       </c>
-      <c r="E25" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E25" s="9"/>
       <c r="F25" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G25" s="1" t="n">
-        <f aca="false">LN(D25/F25)/E25</f>
+        <v>0.52</v>
+      </c>
+      <c r="H25" s="1" t="n">
+        <f aca="false">LN(D25/G25)/F25</f>
         <v>29.7670108389214</v>
       </c>
-      <c r="H25" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I25" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J25" s="1" t="n">
-        <f aca="false">LN(D25/I25)/H25</f>
+        <v>0.55</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <f aca="false">LN(D25/J25)/I25</f>
         <v>24.7133026240606</v>
       </c>
-      <c r="K25" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L25" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M25" s="1" t="n">
-        <f aca="false">LN(D25/L25)/K25</f>
+        <v>0.5</v>
+      </c>
+      <c r="N25" s="1" t="n">
+        <f aca="false">LN(D25/M25)/L25</f>
         <v>36.5048272697714</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>672.05</v>
@@ -1497,40 +1528,41 @@
       <c r="D26" s="9" t="n">
         <v>3.60362432556304</v>
       </c>
-      <c r="E26" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E26" s="9"/>
       <c r="F26" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G26" s="1" t="n">
-        <f aca="false">LN(D26/F26)/E26</f>
+        <v>0.52</v>
+      </c>
+      <c r="H26" s="1" t="n">
+        <f aca="false">LN(D26/G26)/F26</f>
         <v>32.2644427254921</v>
       </c>
-      <c r="H26" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I26" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J26" s="1" t="n">
-        <f aca="false">LN(D26/I26)/H26</f>
+        <v>0.55</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <f aca="false">LN(D26/J26)/I26</f>
         <v>26.8539585268354</v>
       </c>
-      <c r="K26" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L26" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M26" s="1" t="n">
-        <f aca="false">LN(D26/L26)/K26</f>
+        <v>0.5</v>
+      </c>
+      <c r="N26" s="1" t="n">
+        <f aca="false">LN(D26/M26)/L26</f>
         <v>39.5017455336561</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>663.55</v>
@@ -1542,40 +1574,41 @@
       <c r="D27" s="9" t="n">
         <v>4.21742361136203</v>
       </c>
-      <c r="E27" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E27" s="9"/>
       <c r="F27" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G27" s="1" t="n">
-        <f aca="false">LN(D27/F27)/E27</f>
+        <v>0.52</v>
+      </c>
+      <c r="H27" s="1" t="n">
+        <f aca="false">LN(D27/G27)/F27</f>
         <v>34.8858481729601</v>
       </c>
-      <c r="H27" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I27" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J27" s="1" t="n">
-        <f aca="false">LN(D27/I27)/H27</f>
+        <v>0.55</v>
+      </c>
+      <c r="K27" s="1" t="n">
+        <f aca="false">LN(D27/J27)/I27</f>
         <v>29.100877481808</v>
       </c>
-      <c r="K27" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L27" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M27" s="1" t="n">
-        <f aca="false">LN(D27/L27)/K27</f>
+        <v>0.5</v>
+      </c>
+      <c r="N27" s="1" t="n">
+        <f aca="false">LN(D27/M27)/L27</f>
         <v>42.6474320706177</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B28" s="8" t="n">
         <v>662.3</v>
@@ -1587,40 +1620,41 @@
       <c r="D28" s="9" t="n">
         <v>4.549971685095</v>
       </c>
-      <c r="E28" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E28" s="9"/>
       <c r="F28" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G28" s="1" t="n">
-        <f aca="false">LN(D28/F28)/E28</f>
+        <v>0.52</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <f aca="false">LN(D28/G28)/F28</f>
         <v>36.1507912882353</v>
       </c>
-      <c r="H28" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I28" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J28" s="1" t="n">
-        <f aca="false">LN(D28/I28)/H28</f>
+        <v>0.55</v>
+      </c>
+      <c r="K28" s="1" t="n">
+        <f aca="false">LN(D28/J28)/I28</f>
         <v>30.1851144377582</v>
       </c>
-      <c r="K28" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L28" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M28" s="1" t="n">
-        <f aca="false">LN(D28/L28)/K28</f>
+        <v>0.5</v>
+      </c>
+      <c r="N28" s="1" t="n">
+        <f aca="false">LN(D28/M28)/L28</f>
         <v>44.1653638089479</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B29" s="8" t="n">
         <v>640.8</v>
@@ -1632,40 +1666,41 @@
       <c r="D29" s="9" t="n">
         <v>4.26436498945524</v>
       </c>
-      <c r="E29" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E29" s="9"/>
       <c r="F29" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G29" s="1" t="n">
-        <f aca="false">LN(D29/F29)/E29</f>
+        <v>0.52</v>
+      </c>
+      <c r="H29" s="1" t="n">
+        <f aca="false">LN(D29/G29)/F29</f>
         <v>35.0703291418196</v>
       </c>
-      <c r="H29" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I29" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J29" s="1" t="n">
-        <f aca="false">LN(D29/I29)/H29</f>
+        <v>0.55</v>
+      </c>
+      <c r="K29" s="1" t="n">
+        <f aca="false">LN(D29/J29)/I29</f>
         <v>29.2590040265448</v>
       </c>
-      <c r="K29" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L29" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M29" s="1" t="n">
-        <f aca="false">LN(D29/L29)/K29</f>
+        <v>0.5</v>
+      </c>
+      <c r="N29" s="1" t="n">
+        <f aca="false">LN(D29/M29)/L29</f>
         <v>42.8688092332492</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B30" s="8" t="n">
         <v>639.05</v>
@@ -1677,40 +1712,41 @@
       <c r="D30" s="9" t="n">
         <v>4.24571087923649</v>
       </c>
-      <c r="E30" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E30" s="9"/>
       <c r="F30" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G30" s="1" t="n">
-        <f aca="false">LN(D30/F30)/E30</f>
+        <v>0.52</v>
+      </c>
+      <c r="H30" s="1" t="n">
+        <f aca="false">LN(D30/G30)/F30</f>
         <v>34.9972622644554</v>
       </c>
-      <c r="H30" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I30" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J30" s="1" t="n">
-        <f aca="false">LN(D30/I30)/H30</f>
+        <v>0.55</v>
+      </c>
+      <c r="K30" s="1" t="n">
+        <f aca="false">LN(D30/J30)/I30</f>
         <v>29.1963752745183</v>
       </c>
-      <c r="K30" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L30" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M30" s="1" t="n">
-        <f aca="false">LN(D30/L30)/K30</f>
+        <v>0.5</v>
+      </c>
+      <c r="N30" s="1" t="n">
+        <f aca="false">LN(D30/M30)/L30</f>
         <v>42.7811289804121</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B31" s="8" t="n">
         <v>637.05</v>
@@ -1722,40 +1758,41 @@
       <c r="D31" s="9" t="n">
         <v>4.43718468026242</v>
       </c>
-      <c r="E31" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E31" s="9"/>
       <c r="F31" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G31" s="1" t="n">
-        <f aca="false">LN(D31/F31)/E31</f>
+        <v>0.52</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <f aca="false">LN(D31/G31)/F31</f>
         <v>35.7324426952405</v>
       </c>
-      <c r="H31" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I31" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J31" s="1" t="n">
-        <f aca="false">LN(D31/I31)/H31</f>
+        <v>0.55</v>
+      </c>
+      <c r="K31" s="1" t="n">
+        <f aca="false">LN(D31/J31)/I31</f>
         <v>29.8265299294769</v>
       </c>
-      <c r="K31" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L31" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M31" s="1" t="n">
-        <f aca="false">LN(D31/L31)/K31</f>
+        <v>0.5</v>
+      </c>
+      <c r="N31" s="1" t="n">
+        <f aca="false">LN(D31/M31)/L31</f>
         <v>43.6633454973542</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B32" s="8" t="n">
         <v>632.55</v>
@@ -1767,40 +1804,41 @@
       <c r="D32" s="9" t="n">
         <v>4.04068246408255</v>
       </c>
-      <c r="E32" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E32" s="9"/>
       <c r="F32" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G32" s="1" t="n">
-        <f aca="false">LN(D32/F32)/E32</f>
+        <v>0.52</v>
+      </c>
+      <c r="H32" s="1" t="n">
+        <f aca="false">LN(D32/G32)/F32</f>
         <v>34.1723345311052</v>
       </c>
-      <c r="H32" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I32" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J32" s="1" t="n">
-        <f aca="false">LN(D32/I32)/H32</f>
+        <v>0.55</v>
+      </c>
+      <c r="K32" s="1" t="n">
+        <f aca="false">LN(D32/J32)/I32</f>
         <v>28.4892943602181</v>
       </c>
-      <c r="K32" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L32" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M32" s="1" t="n">
-        <f aca="false">LN(D32/L32)/K32</f>
+        <v>0.5</v>
+      </c>
+      <c r="N32" s="1" t="n">
+        <f aca="false">LN(D32/M32)/L32</f>
         <v>41.7912157003919</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B33" s="8" t="n">
         <v>628.1</v>
@@ -1812,40 +1850,41 @@
       <c r="D33" s="9" t="n">
         <v>4.15798148951786</v>
       </c>
-      <c r="E33" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E33" s="9"/>
       <c r="F33" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G33" s="1" t="n">
-        <f aca="false">LN(D33/F33)/E33</f>
+        <v>0.52</v>
+      </c>
+      <c r="H33" s="1" t="n">
+        <f aca="false">LN(D33/G33)/F33</f>
         <v>34.6492700842862</v>
       </c>
-      <c r="H33" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I33" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J33" s="1" t="n">
-        <f aca="false">LN(D33/I33)/H33</f>
+        <v>0.55</v>
+      </c>
+      <c r="K33" s="1" t="n">
+        <f aca="false">LN(D33/J33)/I33</f>
         <v>28.8980962629447</v>
       </c>
-      <c r="K33" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L33" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M33" s="1" t="n">
-        <f aca="false">LN(D33/L33)/K33</f>
+        <v>0.5</v>
+      </c>
+      <c r="N33" s="1" t="n">
+        <f aca="false">LN(D33/M33)/L33</f>
         <v>42.363538364209</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B34" s="8" t="n">
         <v>623.45</v>
@@ -1857,40 +1896,41 @@
       <c r="D34" s="9" t="n">
         <v>3.73427105157719</v>
       </c>
-      <c r="E34" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E34" s="9"/>
       <c r="F34" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G34" s="1" t="n">
-        <f aca="false">LN(D34/F34)/E34</f>
+        <v>0.52</v>
+      </c>
+      <c r="H34" s="1" t="n">
+        <f aca="false">LN(D34/G34)/F34</f>
         <v>32.8579850005028</v>
       </c>
-      <c r="H34" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I34" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J34" s="1" t="n">
-        <f aca="false">LN(D34/I34)/H34</f>
+        <v>0.55</v>
+      </c>
+      <c r="K34" s="1" t="n">
+        <f aca="false">LN(D34/J34)/I34</f>
         <v>27.3627090482732</v>
       </c>
-      <c r="K34" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L34" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M34" s="1" t="n">
-        <f aca="false">LN(D34/L34)/K34</f>
+        <v>0.5</v>
+      </c>
+      <c r="N34" s="1" t="n">
+        <f aca="false">LN(D34/M34)/L34</f>
         <v>40.213996263669</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B35" s="8" t="n">
         <v>621.3</v>
@@ -1902,40 +1942,41 @@
       <c r="D35" s="9" t="n">
         <v>3.63158905746091</v>
       </c>
-      <c r="E35" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E35" s="9"/>
       <c r="F35" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G35" s="1" t="n">
-        <f aca="false">LN(D35/F35)/E35</f>
+        <v>0.52</v>
+      </c>
+      <c r="H35" s="1" t="n">
+        <f aca="false">LN(D35/G35)/F35</f>
         <v>32.3932796128687</v>
       </c>
-      <c r="H35" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I35" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J35" s="1" t="n">
-        <f aca="false">LN(D35/I35)/H35</f>
+        <v>0.55</v>
+      </c>
+      <c r="K35" s="1" t="n">
+        <f aca="false">LN(D35/J35)/I35</f>
         <v>26.9643901445868</v>
       </c>
-      <c r="K35" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L35" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M35" s="1" t="n">
-        <f aca="false">LN(D35/L35)/K35</f>
+        <v>0.5</v>
+      </c>
+      <c r="N35" s="1" t="n">
+        <f aca="false">LN(D35/M35)/L35</f>
         <v>39.656349798508</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B36" s="8" t="n">
         <v>618.05</v>
@@ -1947,40 +1988,41 @@
       <c r="D36" s="9" t="n">
         <v>3.57875077812172</v>
       </c>
-      <c r="E36" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E36" s="9"/>
       <c r="F36" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G36" s="1" t="n">
-        <f aca="false">LN(D36/F36)/E36</f>
+        <v>0.52</v>
+      </c>
+      <c r="H36" s="1" t="n">
+        <f aca="false">LN(D36/G36)/F36</f>
         <v>32.1490043710864</v>
       </c>
-      <c r="H36" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I36" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J36" s="1" t="n">
-        <f aca="false">LN(D36/I36)/H36</f>
+        <v>0.55</v>
+      </c>
+      <c r="K36" s="1" t="n">
+        <f aca="false">LN(D36/J36)/I36</f>
         <v>26.7550113659163</v>
       </c>
-      <c r="K36" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L36" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M36" s="1" t="n">
-        <f aca="false">LN(D36/L36)/K36</f>
+        <v>0.5</v>
+      </c>
+      <c r="N36" s="1" t="n">
+        <f aca="false">LN(D36/M36)/L36</f>
         <v>39.3632195083693</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B37" s="8" t="n">
         <v>613.75</v>
@@ -1992,40 +2034,41 @@
       <c r="D37" s="9" t="n">
         <v>3.70681557577653</v>
       </c>
-      <c r="E37" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E37" s="9"/>
       <c r="F37" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G37" s="1" t="n">
-        <f aca="false">LN(D37/F37)/E37</f>
+        <v>0.52</v>
+      </c>
+      <c r="H37" s="1" t="n">
+        <f aca="false">LN(D37/G37)/F37</f>
         <v>32.7349940012512</v>
       </c>
-      <c r="H37" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I37" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J37" s="1" t="n">
-        <f aca="false">LN(D37/I37)/H37</f>
+        <v>0.55</v>
+      </c>
+      <c r="K37" s="1" t="n">
+        <f aca="false">LN(D37/J37)/I37</f>
         <v>27.2572881917718</v>
       </c>
-      <c r="K37" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L37" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M37" s="1" t="n">
-        <f aca="false">LN(D37/L37)/K37</f>
+        <v>0.5</v>
+      </c>
+      <c r="N37" s="1" t="n">
+        <f aca="false">LN(D37/M37)/L37</f>
         <v>40.066407064567</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B38" s="8" t="n">
         <v>599.2</v>
@@ -2037,40 +2080,41 @@
       <c r="D38" s="9" t="n">
         <v>4.34765522271977</v>
       </c>
-      <c r="E38" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E38" s="9"/>
       <c r="F38" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G38" s="1" t="n">
-        <f aca="false">LN(D38/F38)/E38</f>
+        <v>0.52</v>
+      </c>
+      <c r="H38" s="1" t="n">
+        <f aca="false">LN(D38/G38)/F38</f>
         <v>35.3927189653156</v>
       </c>
-      <c r="H38" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I38" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J38" s="1" t="n">
-        <f aca="false">LN(D38/I38)/H38</f>
+        <v>0.55</v>
+      </c>
+      <c r="K38" s="1" t="n">
+        <f aca="false">LN(D38/J38)/I38</f>
         <v>29.5353381609699</v>
       </c>
-      <c r="K38" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L38" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M38" s="1" t="n">
-        <f aca="false">LN(D38/L38)/K38</f>
+        <v>0.5</v>
+      </c>
+      <c r="N38" s="1" t="n">
+        <f aca="false">LN(D38/M38)/L38</f>
         <v>43.2556770214443</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B39" s="8" t="n">
         <v>684.3</v>
@@ -2082,40 +2126,41 @@
       <c r="D39" s="10" t="n">
         <v>3.57945383315914</v>
       </c>
-      <c r="E39" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E39" s="10"/>
       <c r="F39" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G39" s="1" t="n">
-        <f aca="false">LN(D39/F39)/E39</f>
+        <v>0.52</v>
+      </c>
+      <c r="H39" s="1" t="n">
+        <f aca="false">LN(D39/G39)/F39</f>
         <v>32.1522782601776</v>
       </c>
-      <c r="H39" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I39" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J39" s="1" t="n">
-        <f aca="false">LN(D39/I39)/H39</f>
+        <v>0.55</v>
+      </c>
+      <c r="K39" s="1" t="n">
+        <f aca="false">LN(D39/J39)/I39</f>
         <v>26.7578175565658</v>
       </c>
-      <c r="K39" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L39" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M39" s="1" t="n">
-        <f aca="false">LN(D39/L39)/K39</f>
+        <v>0.5</v>
+      </c>
+      <c r="N39" s="1" t="n">
+        <f aca="false">LN(D39/M39)/L39</f>
         <v>39.3671481752787</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B40" s="8" t="n">
         <v>673.05</v>
@@ -2127,40 +2172,41 @@
       <c r="D40" s="10" t="n">
         <v>3.43998697138814</v>
       </c>
-      <c r="E40" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E40" s="10"/>
       <c r="F40" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G40" s="1" t="n">
-        <f aca="false">LN(D40/F40)/E40</f>
+        <v>0.52</v>
+      </c>
+      <c r="H40" s="1" t="n">
+        <f aca="false">LN(D40/G40)/F40</f>
         <v>31.4899025232939</v>
       </c>
-      <c r="H40" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I40" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J40" s="1" t="n">
-        <f aca="false">LN(D40/I40)/H40</f>
+        <v>0.55</v>
+      </c>
+      <c r="K40" s="1" t="n">
+        <f aca="false">LN(D40/J40)/I40</f>
         <v>26.1900669249512</v>
       </c>
-      <c r="K40" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L40" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M40" s="1" t="n">
-        <f aca="false">LN(D40/L40)/K40</f>
+        <v>0.5</v>
+      </c>
+      <c r="N40" s="1" t="n">
+        <f aca="false">LN(D40/M40)/L40</f>
         <v>38.5722972910182</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B41" s="8" t="n">
         <v>663.55</v>
@@ -2172,40 +2218,41 @@
       <c r="D41" s="10" t="n">
         <v>5.47999509259563</v>
       </c>
-      <c r="E41" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E41" s="10"/>
       <c r="F41" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G41" s="1" t="n">
-        <f aca="false">LN(D41/F41)/E41</f>
+        <v>0.52</v>
+      </c>
+      <c r="H41" s="1" t="n">
+        <f aca="false">LN(D41/G41)/F41</f>
         <v>39.2505112142407</v>
       </c>
-      <c r="H41" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I41" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J41" s="1" t="n">
-        <f aca="false">LN(D41/I41)/H41</f>
+        <v>0.55</v>
+      </c>
+      <c r="K41" s="1" t="n">
+        <f aca="false">LN(D41/J41)/I41</f>
         <v>32.8420172314771</v>
       </c>
-      <c r="K41" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L41" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M41" s="1" t="n">
-        <f aca="false">LN(D41/L41)/K41</f>
+        <v>0.5</v>
+      </c>
+      <c r="N41" s="1" t="n">
+        <f aca="false">LN(D41/M41)/L41</f>
         <v>47.8850277201544</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B42" s="5" t="n">
         <v>663.05</v>
@@ -2217,40 +2264,41 @@
       <c r="D42" s="11" t="n">
         <v>4.4371838096695</v>
       </c>
-      <c r="E42" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E42" s="11"/>
       <c r="F42" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G42" s="1" t="n">
-        <f aca="false">LN(D42/F42)/E42</f>
+        <v>0.52</v>
+      </c>
+      <c r="H42" s="1" t="n">
+        <f aca="false">LN(D42/G42)/F42</f>
         <v>35.7324394251752</v>
       </c>
-      <c r="H42" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I42" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J42" s="1" t="n">
-        <f aca="false">LN(D42/I42)/H42</f>
+        <v>0.55</v>
+      </c>
+      <c r="K42" s="1" t="n">
+        <f aca="false">LN(D42/J42)/I42</f>
         <v>29.8265271265639</v>
       </c>
-      <c r="K42" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L42" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M42" s="1" t="n">
-        <f aca="false">LN(D42/L42)/K42</f>
+        <v>0.5</v>
+      </c>
+      <c r="N42" s="1" t="n">
+        <f aca="false">LN(D42/M42)/L42</f>
         <v>43.6633415732759</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B43" s="5" t="n">
         <v>662.3</v>
@@ -2262,40 +2310,41 @@
       <c r="D43" s="11" t="n">
         <v>5.16696117670098</v>
       </c>
-      <c r="E43" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E43" s="11"/>
       <c r="F43" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G43" s="1" t="n">
-        <f aca="false">LN(D43/F43)/E43</f>
+        <v>0.52</v>
+      </c>
+      <c r="H43" s="1" t="n">
+        <f aca="false">LN(D43/G43)/F43</f>
         <v>38.2701867163555</v>
       </c>
-      <c r="H43" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I43" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J43" s="1" t="n">
-        <f aca="false">LN(D43/I43)/H43</f>
+        <v>0.55</v>
+      </c>
+      <c r="K43" s="1" t="n">
+        <f aca="false">LN(D43/J43)/I43</f>
         <v>32.0017390904327</v>
       </c>
-      <c r="K43" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L43" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M43" s="1" t="n">
-        <f aca="false">LN(D43/L43)/K43</f>
+        <v>0.5</v>
+      </c>
+      <c r="N43" s="1" t="n">
+        <f aca="false">LN(D43/M43)/L43</f>
         <v>46.7086383226923</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B44" s="5" t="n">
         <v>656.15</v>
@@ -2307,40 +2356,41 @@
       <c r="D44" s="11" t="n">
         <v>4.97785238565978</v>
       </c>
-      <c r="E44" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E44" s="11"/>
       <c r="F44" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G44" s="1" t="n">
-        <f aca="false">LN(D44/F44)/E44</f>
+        <v>0.52</v>
+      </c>
+      <c r="H44" s="1" t="n">
+        <f aca="false">LN(D44/G44)/F44</f>
         <v>37.6487502928274</v>
       </c>
-      <c r="H44" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I44" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J44" s="1" t="n">
-        <f aca="false">LN(D44/I44)/H44</f>
+        <v>0.55</v>
+      </c>
+      <c r="K44" s="1" t="n">
+        <f aca="false">LN(D44/J44)/I44</f>
         <v>31.4690792988371</v>
       </c>
-      <c r="K44" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L44" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M44" s="1" t="n">
-        <f aca="false">LN(D44/L44)/K44</f>
+        <v>0.5</v>
+      </c>
+      <c r="N44" s="1" t="n">
+        <f aca="false">LN(D44/M44)/L44</f>
         <v>45.9629146144585</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B45" s="5" t="n">
         <v>653.8</v>
@@ -2352,40 +2402,41 @@
       <c r="D45" s="11" t="n">
         <v>5.04623074934568</v>
       </c>
-      <c r="E45" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E45" s="11"/>
       <c r="F45" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G45" s="1" t="n">
-        <f aca="false">LN(D45/F45)/E45</f>
+        <v>0.52</v>
+      </c>
+      <c r="H45" s="1" t="n">
+        <f aca="false">LN(D45/G45)/F45</f>
         <v>37.8761340956807</v>
       </c>
-      <c r="H45" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I45" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J45" s="1" t="n">
-        <f aca="false">LN(D45/I45)/H45</f>
+        <v>0.55</v>
+      </c>
+      <c r="K45" s="1" t="n">
+        <f aca="false">LN(D45/J45)/I45</f>
         <v>31.6639797012828</v>
       </c>
-      <c r="K45" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L45" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M45" s="1" t="n">
-        <f aca="false">LN(D45/L45)/K45</f>
+        <v>0.5</v>
+      </c>
+      <c r="N45" s="1" t="n">
+        <f aca="false">LN(D45/M45)/L45</f>
         <v>46.2357751778824</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B46" s="5" t="n">
         <v>639.1</v>
@@ -2397,40 +2448,41 @@
       <c r="D46" s="11" t="n">
         <v>5.0678031906316</v>
       </c>
-      <c r="E46" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E46" s="11"/>
       <c r="F46" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G46" s="1" t="n">
-        <f aca="false">LN(D46/F46)/E46</f>
+        <v>0.52</v>
+      </c>
+      <c r="H46" s="1" t="n">
+        <f aca="false">LN(D46/G46)/F46</f>
         <v>37.9472315896104</v>
       </c>
-      <c r="H46" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I46" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J46" s="1" t="n">
-        <f aca="false">LN(D46/I46)/H46</f>
+        <v>0.55</v>
+      </c>
+      <c r="K46" s="1" t="n">
+        <f aca="false">LN(D46/J46)/I46</f>
         <v>31.7249204103654</v>
       </c>
-      <c r="K46" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L46" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M46" s="1" t="n">
-        <f aca="false">LN(D46/L46)/K46</f>
+        <v>0.5</v>
+      </c>
+      <c r="N46" s="1" t="n">
+        <f aca="false">LN(D46/M46)/L46</f>
         <v>46.3210921705981</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B47" s="5" t="n">
         <v>617.8</v>
@@ -2442,34 +2494,35 @@
       <c r="D47" s="11" t="n">
         <v>4.09874678583355</v>
       </c>
-      <c r="E47" s="1" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="E47" s="11"/>
       <c r="F47" s="1" t="n">
-        <v>0.52</v>
+        <v>0.06</v>
       </c>
       <c r="G47" s="1" t="n">
-        <f aca="false">LN(D47/F47)/E47</f>
+        <v>0.52</v>
+      </c>
+      <c r="H47" s="1" t="n">
+        <f aca="false">LN(D47/G47)/F47</f>
         <v>34.4101288733494</v>
       </c>
-      <c r="H47" s="1" t="n">
-        <v>0.07</v>
-      </c>
       <c r="I47" s="1" t="n">
-        <v>0.55</v>
+        <v>0.07</v>
       </c>
       <c r="J47" s="1" t="n">
-        <f aca="false">LN(D47/I47)/H47</f>
+        <v>0.55</v>
+      </c>
+      <c r="K47" s="1" t="n">
+        <f aca="false">LN(D47/J47)/I47</f>
         <v>28.6931180821417</v>
       </c>
-      <c r="K47" s="1" t="n">
-        <v>0.05</v>
-      </c>
       <c r="L47" s="1" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="M47" s="1" t="n">
-        <f aca="false">LN(D47/L47)/K47</f>
+        <v>0.5</v>
+      </c>
+      <c r="N47" s="1" t="n">
+        <f aca="false">LN(D47/M47)/L47</f>
         <v>42.0765689110848</v>
       </c>
     </row>
